--- a/picSpss/39-2-打字訓練-40.xlsx
+++ b/picSpss/39-2-打字訓練-40.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Website\lecture\CRM\picSpss\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{B5DB1243-9E76-48EF-A79A-4A1CEAFEA66E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97D99376-4686-4FDD-A3C4-68C18B03B170}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{EF8EEFE8-C9B2-4E32-9B27-6058B010BBAC}"/>
+    <workbookView xWindow="1400" yWindow="1400" windowWidth="14380" windowHeight="7330" xr2:uid="{EF8EEFE8-C9B2-4E32-9B27-6058B010BBAC}"/>
   </bookViews>
   <sheets>
     <sheet name="39-2-打字訓練" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>訓練後-40</t>
+    <t>訓練後減40</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
